--- a/extenbooks/S507.xlsx
+++ b/extenbooks/S507.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_5_8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -986,54 +990,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S507-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S507 — Surplus Ratio (S*/Y = S*/(S*+V*))</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix —</t>
+          <t># S507 — Surplus Ratio (S*/Y = S*/(S*+V*))</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: ratio</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via n/a (book period only) when API access provisioned)</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1046,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix —</t>
         </is>
       </c>
     </row>
@@ -1049,291 +1054,291 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Units**: ratio</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1989 (book period; extension via n/a (book period only) when API access provisioned)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Surplus Ratio S*/(S*+V*). Derived from S505 and S504 directly; no source column. Equivalent to S*/VA*.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Surplus Ratio S*/(S*+V*). Derived from S505 and S504 directly; no source column. Equivalent to S*/VA*.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>| `S507-A` | S&amp;T 1994 | 1948-1989 | ratio |</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>| Subseries | Source | Period | Units |</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>| `S507-A` | S&amp;T 1994 | 1948-1989 | ratio |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>### S507-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/(derived from S505 and S504)`.</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2. Load S505-A and S504-A from `data/final/`.</t>
+          <t>### S507-A (book period, 1948-1989)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>3. Compute year-by-year: value = S_star / (S_star + V_star).</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/(derived from S505 and S504)`.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Validator checks against book-published surplus ratios at benchmark years.</t>
+          <t>2. Load S505-A and S504-A from `data/final/`.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3. Compute year-by-year: value = S_star / (S_star + V_star).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Validator checks against book-published surplus ratios at benchmark years.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1948=0.57, 1989=0.60</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Tolerance class: `rate_series` (rel 0.001 / abs 0.01).</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1948=0.57, 1989=0.60</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S507_surplus_ratio.py` writes to `data/intermediate/validation/S507.json`.</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Tolerance class: `rate_series` (rel 0.001 / abs 0.01).</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S507_surplus_ratio.py` writes to `data/intermediate/validation/S507.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>data/source/book_tables/(derived from S505 and S504)</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S507_surplus_ratio.py</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S507.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1346,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S507_surplus_ratio.py</t>
+          <t>data/source/book_tables/(derived from S505 and S504)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1354,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S507.csv</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S507_surplus_ratio.py</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1362,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S507_surplus_ratio.py</t>
+          <t xml:space="preserve">       └── data/intermediate/S507.csv</t>
         </is>
       </c>
     </row>
@@ -1365,65 +1370,89 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S507_surplus_ratio.py</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S507.csv</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S507_surplus_ratio.py</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>## Citations</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Derived measure; book-period benchmarks from validation_config.json.</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Derived measure; book-period benchmarks from validation_config.json.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1440,10 +1469,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1468,209 +1497,342 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S*/Y = S*/(S* + V*), where Y = S* + V* = GFP. The surplus ratio expresses surplus value as a share of the net product (value-added of productive sectors). It is a monotonic transform of the exploitation rate: S*/Y = e/(1+e).</t>
+          <t>The rate of exploitation is the ratio of surplus labor time to necessary labor time. This concept applies to all capitalistically employed wage labor, whether it is productive or unproductive (Shaikh 1978b, p. 21).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 Table 5.7; Knowledge_Base/equations/page_310_equations.txt</t>
+          <t>ST_1994, Ch4 Sec 4.2, p.87; chunk_11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Derived from S505 and S504: S*/Y = S505/(S505 + S504). Presented in Table 5.7 alongside the exploitation rate. No independent extension — follows from S505 and S504 availability.</t>
+          <t>However, observed differences in money and labor value ratios will be indicators of price-value deviations only if the mapping involved is consistent in the sense just described. If it is not, then the two sets of magnitudes would differ even when purchaser prices are equal to labor values, simply because the calculation procedure is inconsistent.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.7</t>
+          <t>ST_1994, Ch4 Sec 4.1, p.84; chunk_11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>theoretical_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The surplus ratio is the Marxian analog to the profit share in orthodox economics, but measured only over the productive sector. It rises secularly as the exploitation rate rises, reflecting the increasing proportion of new value captured as surplus rather than wages.</t>
+          <t>Money rate S*/V* and labor value rate S/V differ by only 6%-9% in all years studied; S*/V* consistently lower than S/V (Khanjian 1989, p. 109, table 19).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 chunk_24-chunk_25</t>
+          <t>ST_1994, Ch4 Sec 4.1, p.84; chunk_11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mohun's employment decomposition and industry classification data (mohun_employment*.csv, mohun_industry_classification.csv) provide alternative frameworks for computing the surplus ratio with different sector boundaries.</t>
+          <t>S* = VA* − V* = surplus value (in money form); S*/V* = rate of surplus value.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No independent extension. The surplus ratio is fully determined by the exploitation rate, so all caveats applying to S506 apply here. Table 5.7 only; no dedicated figure in the book.</t>
+          <t>For U.S. data, the orthodox measure VA = P + EC remains within 10% of the Marxian measure VA* = V* + S*.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPR T507_DPR.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEC-003: The VA*/W constant assumption (ec_u/ec_p ≈ 1.238) propagates directly into S507 because S507 is a monotonic transform of the exploitation rate (S506). The partial resolution in Session 14 (year-varying ec_u/ec_p) reduces but does not eliminate the systematic error. The SIC-era gap (1990-1997) is handled by log-linear interpolation (DEC-007). S507 extension values carry the same systematic error as S506.</t>
+          <t>This latter movement [of the surplus ratio] is a reflection of the corresponding decline in productive to total wages, because S* = VA* − Wp = VA* − ECp and (P⁺) = NNP − EC = VA − EC, and the two measures of value added remain fairly close.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-003 (2025-12-05, partially resolved 2026-03-30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S*/Y = S*/(S* + V*), where Y = S* + V* = GFP. The surplus ratio expresses surplus value as a share of the net product (value-added of productive sectors). It is a monotonic transform of the exploitation rate: S*/Y = e/(1+e).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 Table 5.7; Knowledge_Base/equations/page_310_equations.txt</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Surplus ratio S*/Y = S*/(S*+V*) = e/(1+e). A monotonic transform of the exploitation rate. Book period only (Table 5.7), no extension. DEC-003: inherits VA*/W constant assumption error from S506.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Derived from S505 and S504: S*/Y = S505/(S505 + S504). Presented in Table 5.7 alongside the exploitation rate. No independent extension — follows from S505 and S504 availability.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Table 5.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>theoretical_note</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The surplus ratio is the Marxian analog to the profit share in orthodox economics, but measured only over the productive sector. It rises secularly as the exploitation rate rises, reflecting the increasing proportion of new value captured as surplus rather than wages.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 chunk_24-chunk_25</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>external_comparison</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mohun's employment decomposition and industry classification data (mohun_employment*.csv, mohun_industry_classification.csv) provide alternative frameworks for computing the surplus ratio with different sector boundaries.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>No independent extension — inherits all S506 issues</t>
+          <t>No independent extension. The surplus ratio is fully determined by the exploitation rate, so all caveats applying to S506 apply here. Table 5.7 only; no dedicated figure in the book.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DPR T507_DPR.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>No dedicated figure in the book</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DEC-003: VA*/W constant carries small systematic error for extension period (1990-1997 interpolated per DEC-007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>[internal-decision-record]: The VA*/W constant assumption (ec_u/ec_p ≈ 1.238) propagates directly into S507 because S507 is a monotonic transform of the exploitation rate (S506). The partial resolution in Session 14 (year-varying ec_u/ec_p) reduces but does not eliminate the systematic error. The SIC-era gap (1990-1997) is handled by log-linear interpolation ([internal-decision-record]). S507 extension values carry the same systematic error as S506.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[internal-decision-log] [internal-decision-record] (2025-12-05, partially resolved 2026-03-30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S504</t>
-        </is>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S505</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S506</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Surplus ratio S*/Y = S*/(S*+V*) = e/(1+e). A monotonic transform of the exploitation rate. Book period only (Table 5.7), no extension. [internal-decision-record]: inherits VA*/W constant assumption error from S506.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>No independent extension — inherits all S506 issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>No dedicated figure in the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[internal-decision-record]: VA*/W constant carries small systematic error for extension period (1990-1997 interpolated per [internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S504</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S505</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
@@ -1687,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1750,7 +1912,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1933,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 0.6296, "1989": 0.7093}</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1957,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.02</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S507.xlsx
+++ b/extenbooks/S507.xlsx
@@ -491,7 +491,7 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.6361379782590089</v>
+        <v>0.6361352557765309</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.6395015865645075</v>
+        <v>0.6394991119142794</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.6399578460701659</v>
+        <v>0.639953495012952</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.6366522649908353</v>
+        <v>0.6366460135570807</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.6353328570097232</v>
+        <v>0.6353368043043354</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.6503201624238638</v>
+        <v>0.65031609985257</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +539,7 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.6547397370154984</v>
+        <v>0.654743488374758</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.647830722545723</v>
+        <v>0.6478236384413085</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +555,7 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.6529680365296804</v>
+        <v>0.6529697402993876</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.6672831948315835</v>
+        <v>0.667288409787765</v>
       </c>
     </row>
     <row r="14">
@@ -595,7 +595,7 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.6730567116492201</v>
+        <v>0.6730623707266215</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +603,7 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.6747857014406458</v>
+        <v>0.6747883980594164</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.6794274425019571</v>
+        <v>0.6794299751368962</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.6770306634900501</v>
+        <v>0.677035305248652</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.6752963683121118</v>
+        <v>0.6752984861647311</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.6775415262577162</v>
+        <v>0.6775445570537548</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.6758351588170866</v>
+        <v>0.6758360841129301</v>
       </c>
     </row>
     <row r="24">
@@ -651,7 +651,7 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.6672568626202152</v>
+        <v>0.667260262455958</v>
       </c>
     </row>
     <row r="25">
@@ -659,7 +659,7 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.6694413885833028</v>
+        <v>0.6694397520113629</v>
       </c>
     </row>
     <row r="26">
@@ -667,7 +667,7 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.6748244235097204</v>
+        <v>0.6748282394187001</v>
       </c>
     </row>
     <row r="27">
@@ -675,7 +675,7 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.6657665828420662</v>
+        <v>0.6657645243707249</v>
       </c>
     </row>
     <row r="28">
@@ -691,7 +691,7 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.6613554280858296</v>
+        <v>0.6613526180045973</v>
       </c>
     </row>
     <row r="30">
@@ -707,7 +707,7 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0.6782316496902236</v>
+        <v>0.6782340237110984</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +715,7 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.6774050308329269</v>
+        <v>0.6774033362018933</v>
       </c>
     </row>
     <row r="33">
@@ -723,7 +723,7 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.6745236898363227</v>
+        <v>0.6745229446182673</v>
       </c>
     </row>
     <row r="34">
@@ -731,7 +731,7 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.6694314328052431</v>
+        <v>0.6694304341621155</v>
       </c>
     </row>
     <row r="35">
@@ -739,7 +739,7 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.6742945653526827</v>
+        <v>0.674295808735466</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.6835331524990371</v>
+        <v>0.6835328724245976</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.6867924227762712</v>
+        <v>0.686792969757981</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +763,7 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.6896245837229674</v>
+        <v>0.6896240739344424</v>
       </c>
     </row>
     <row r="39">
@@ -779,7 +779,7 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.7000034090873872</v>
+        <v>0.7000027582590489</v>
       </c>
     </row>
     <row r="41">
@@ -787,7 +787,7 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.7062794514745593</v>
+        <v>0.7062802824756388</v>
       </c>
     </row>
     <row r="42">
@@ -795,7 +795,7 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0.7072797907446444</v>
+        <v>0.707279595594271</v>
       </c>
     </row>
     <row r="43">
@@ -803,7 +803,7 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0.706024318869052</v>
+        <v>0.7060239567154103</v>
       </c>
     </row>
     <row r="44">
@@ -811,7 +811,7 @@
         <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0.7092836917886619</v>
+        <v>0.7092843754774388</v>
       </c>
     </row>
   </sheetData>

--- a/extenbooks/S507.xlsx
+++ b/extenbooks/S507.xlsx
@@ -1849,11 +1849,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1997,6 +1997,18 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>reference_source</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>identity-derived from book e: S*/(S*+V*) = e/(1+e); class=identity (book-derived, NOT tautological).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
